--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_wolf_soul.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_wolf_soul.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_wolf_soul.xlsx" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="80">
   <si>
     <t>id</t>
   </si>
@@ -287,12 +287,6 @@
   </si>
   <si>
     <t>15#10#5|10#5#5|5#5|4#6#4#2#4|1#7#2#6</t>
-  </si>
-  <si>
-    <t>15001001#5|15001002#5|15001003#10|15001004#5|15001005#5|15001006#10|15001007#15|15001008#15|15001009#20|15001010#15|15001011#15|15001012#20|15001013#25|15001014#25|15001015#30|15001016#25|15001017#25|15001018#30|15001019#35|15001020#35|15001021#40|15001022#35|15001023#35|15001024#40|15001025#45|15001026#45|15001027#50|15001028#45|15001029#45|15001030#50</t>
-  </si>
-  <si>
-    <t>1#1#10020001#30000#10120001#750|2#2#10020001#24000#10120001#675|3#3#10020001#18000#10120001#600|4#10#10020001#15000#10120001#525|11#20#10020001#9000#10120001#450|21#50#10020001#6000#10120001#375|51#999#10020001#3000#10120001#300</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1366,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="138" customHeight="1" spans="4:22">
+    <row r="2" s="1" customFormat="1" ht="138" customHeight="1" spans="1:22">
       <c r="D2" s="2" t="s">
         <v>22</v>
       </c>
@@ -1625,15 +1619,9 @@
       <c r="S5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="T5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
